--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_saldomigr_a_2020_biobio.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_saldomigr_a_2020_biobio.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:11</t>
+    <t xml:space="preserve">2026-09-24 01:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -685,7 +685,7 @@
         <v>0.15</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>-0.3</v>
@@ -708,7 +708,7 @@
         <v>-0.03</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>0.12</v>
@@ -731,7 +731,7 @@
         <v>-0.01</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>0.11</v>
@@ -800,7 +800,7 @@
         <v>0.2</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>-0.1</v>
@@ -823,7 +823,7 @@
         <v>0.13</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>-0.04</v>
@@ -892,7 +892,7 @@
         <v>-0.09</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>-0.18</v>
@@ -915,7 +915,7 @@
         <v>-0.1</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>-0.25</v>
@@ -961,10 +961,10 @@
         <v>0.16</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="20">
@@ -984,7 +984,7 @@
         <v>0.13</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0.19</v>
@@ -1007,7 +1007,7 @@
         <v>0.09</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>-0.3</v>
@@ -1021,7 +1021,7 @@
         <v>28</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>-0.3</v>
+        <v>-0.31</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>33</v>
@@ -1030,7 +1030,7 @@
         <v>0.01</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>-0.31</v>
@@ -1053,7 +1053,7 @@
         <v>-0.08</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>0.37</v>
@@ -1076,7 +1076,7 @@
         <v>-0.36</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>0.49</v>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_saldomigr_a_2020_biobio.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_saldomigr_a_2020_biobio.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:01</t>
+    <t xml:space="preserve">2026-10-01 23:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_saldomigr_a_2020_biobio.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_saldomigr_a_2020_biobio.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:10</t>
+    <t xml:space="preserve">2026-10-05 19:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
